--- a/templates/BenchmarkV3/master.xlsx
+++ b/templates/BenchmarkV3/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mosch\Bureau\KAIVAA\kaivaa-builder\templates\BenchmarkV3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434F84DF-3986-4BD8-94E5-8538E4B79926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F585FB9-3A52-4854-B31A-81DA6A58A514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{1FFF5854-B54B-4C80-B65C-C43C5EF7384C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{1FFF5854-B54B-4C80-B65C-C43C5EF7384C}"/>
   </bookViews>
   <sheets>
     <sheet name="DONNÉES BRUTES" sheetId="26" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="159">
   <si>
     <t>Marque</t>
   </si>
@@ -201,9 +201,6 @@
   </si>
   <si>
     <t>confidentiality</t>
-  </si>
-  <si>
-    <t>Entreprises.Nom</t>
   </si>
   <si>
     <t>Public</t>
@@ -338,9 +335,6 @@
     <t>Fabrication de cacao, chocolat et de produits de confiserie</t>
   </si>
   <si>
-    <t>LUTTI</t>
-  </si>
-  <si>
     <t>Fabrication de condiments et assaisonnements</t>
   </si>
   <si>
@@ -468,12 +462,6 @@
   </si>
   <si>
     <t>[Segment]</t>
-  </si>
-  <si>
-    <t>Entreprises.Activité</t>
-  </si>
-  <si>
-    <t>Entreprises.Activité détaillée</t>
   </si>
   <si>
     <t>19,46</t>
@@ -938,7 +926,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="28">
     <dxf>
       <font>
         <b val="0"/>
@@ -1229,9 +1217,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
@@ -1455,10 +1440,10 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>-9.3437831196943724E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0934378311969437</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1580,10 +1565,10 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>-4.5226629920854071E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0452266299208541</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1759,7 +1744,7 @@
                 <c:formatCode>yyyy</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>44196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1771,7 +1756,7 @@
                 <c:formatCode>#\ ##0.0\ \ "M€"</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>64657526</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5930,7 +5915,7 @@
                 <c:formatCode>yyyy</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>44196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5955,7 +5940,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="144"/>
                   <c:pt idx="0">
-                    <c:v>-</c:v>
+                    <c:v>#REF!</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -10096,7 +10081,7 @@
                 <c:formatCode>yyyy</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>44196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10121,7 +10106,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="144"/>
                   <c:pt idx="0">
-                    <c:v>-</c:v>
+                    <c:v>#REF!</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -10535,7 +10520,7 @@
                 <c:formatCode>yyyy</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>44196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10547,7 +10532,7 @@
                 <c:formatCode>#\ ##0.0\ \ "M€"</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>-6041459</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14706,7 +14691,7 @@
                 <c:formatCode>yyyy</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>44196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14731,7 +14716,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="144"/>
                   <c:pt idx="0">
-                    <c:v>-</c:v>
+                    <c:v>#REF!</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -18872,7 +18857,7 @@
                 <c:formatCode>yyyy</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>44196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18897,7 +18882,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="144"/>
                   <c:pt idx="0">
-                    <c:v>-</c:v>
+                    <c:v>#REF!</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -19204,7 +19189,7 @@
                 <c:formatCode>yyyy</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>44196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19216,7 +19201,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="144"/>
                 <c:pt idx="0">
-                  <c:v>-9.3437831196943724E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20732,35 +20717,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{79E1CCFD-C29F-4239-8558-4F70F8B05FAD}" name="Performance" displayName="Performance" ref="A1:Z2" totalsRowShown="0">
-  <autoFilter ref="A1:Z2" xr:uid="{79E1CCFD-C29F-4239-8558-4F70F8B05FAD}"/>
-  <tableColumns count="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{79E1CCFD-C29F-4239-8558-4F70F8B05FAD}" name="Performance" displayName="Performance" ref="A1:W2" totalsRowShown="0">
+  <autoFilter ref="A1:W2" xr:uid="{79E1CCFD-C29F-4239-8558-4F70F8B05FAD}"/>
+  <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{D9C00F17-D0B9-47E9-BDD3-4D9C5C0FDED0}" name="siren"/>
-    <tableColumn id="2" xr3:uid="{72D0A89F-A76F-4AC4-9D3A-4CD3F1A55A5C}" name="date_cloture_exercice" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{72D0A89F-A76F-4AC4-9D3A-4CD3F1A55A5C}" name="date_cloture_exercice" dataDxfId="27"/>
     <tableColumn id="3" xr3:uid="{3EFD615F-AA2D-459F-B4C7-CFFC22318CC1}" name="Chiffre_d_affaires"/>
     <tableColumn id="4" xr3:uid="{80D73410-97C6-4D40-9128-262383E6524C}" name="Marge_brute"/>
     <tableColumn id="5" xr3:uid="{BAD7E762-9FF1-435B-A3F1-352C048EA546}" name="EBE"/>
     <tableColumn id="6" xr3:uid="{3AF3575F-1844-41FF-902F-8EAB8DDD5AD6}" name="EBIT"/>
     <tableColumn id="7" xr3:uid="{C1B7C2D3-EE50-4B20-83E8-6C6C35F45488}" name="Resultat_net"/>
-    <tableColumn id="8" xr3:uid="{1537CC23-C56D-4EB0-B2A3-95305DB00ACE}" name="Taux_d_endettement" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{536AB2AA-44A8-4F01-8C02-46AFBC6DCAA0}" name="Ratio_de_liquidite" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{FBB19A9A-781C-4896-8A9D-2E1318B24C2B}" name="Ratio_de_vetuste" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{B24A4AA8-9886-4D06-B600-7EC30685FA70}" name="Autonomie_financiere" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{3DB745D5-0419-424E-91C4-B9924D399823}" name="Poids_BFR_exploitation_sur_CA" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{53244D27-3DA2-40CA-8077-20C618624F8D}" name="Couverture_des_interets" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{AB0C9F90-5099-48B9-8487-E86268E4FC91}" name="CAF_sur_CA" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{376D6488-15D4-4F0E-8B09-3E8988FBC4CF}" name="Capacite_de_remboursement" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{D16DFA2E-40D3-4F97-8394-8C21A8C82489}" name="Marge_EBE" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{B1B27CBE-8F94-4970-B010-0C617FFCFEBD}" name="Resultat_courant_avant_impots_sur_CA" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{A7078D23-5164-48BC-A4A8-CFC46C4EAB2D}" name="Poids_BFR_exploitation_sur_CA_jours" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{A23C5DCA-B7DD-4EF2-9126-AED71042D7EC}" name="Rotation_des_stocks_jours" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{367BA43D-2822-4E6B-84EA-9C8D94FFB913}" name="Credit_clients_Jours" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{67FEC185-0EAF-4CAF-A9E3-D005531B61AC}" name="Credit_fournisseurs_Jours" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{AF3E4C10-4D82-4995-9FFA-7E2CE8CB46A2}" name="type_bilan" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{465A446E-7698-4C88-BB95-D9C31EA7A990}" name="confidentiality" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{7E0EE648-DC7A-4C10-AE55-84039A393AD9}" name="Entreprises.Nom" dataDxfId="11"/>
-    <tableColumn id="25" xr3:uid="{03B03CBA-639B-4937-9583-2135A393ADA7}" name="Entreprises.Activité"/>
-    <tableColumn id="26" xr3:uid="{011A9113-0055-4B4B-9BB8-F00CE3094B88}" name="Entreprises.Activité détaillée"/>
+    <tableColumn id="8" xr3:uid="{1537CC23-C56D-4EB0-B2A3-95305DB00ACE}" name="Taux_d_endettement" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{536AB2AA-44A8-4F01-8C02-46AFBC6DCAA0}" name="Ratio_de_liquidite" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{FBB19A9A-781C-4896-8A9D-2E1318B24C2B}" name="Ratio_de_vetuste" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{B24A4AA8-9886-4D06-B600-7EC30685FA70}" name="Autonomie_financiere" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{3DB745D5-0419-424E-91C4-B9924D399823}" name="Poids_BFR_exploitation_sur_CA" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{53244D27-3DA2-40CA-8077-20C618624F8D}" name="Couverture_des_interets" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{AB0C9F90-5099-48B9-8487-E86268E4FC91}" name="CAF_sur_CA" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{376D6488-15D4-4F0E-8B09-3E8988FBC4CF}" name="Capacite_de_remboursement" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{D16DFA2E-40D3-4F97-8394-8C21A8C82489}" name="Marge_EBE" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{B1B27CBE-8F94-4970-B010-0C617FFCFEBD}" name="Resultat_courant_avant_impots_sur_CA" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{A7078D23-5164-48BC-A4A8-CFC46C4EAB2D}" name="Poids_BFR_exploitation_sur_CA_jours" dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{A23C5DCA-B7DD-4EF2-9126-AED71042D7EC}" name="Rotation_des_stocks_jours" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{367BA43D-2822-4E6B-84EA-9C8D94FFB913}" name="Credit_clients_Jours" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{67FEC185-0EAF-4CAF-A9E3-D005531B61AC}" name="Credit_fournisseurs_Jours" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{AF3E4C10-4D82-4995-9FFA-7E2CE8CB46A2}" name="type_bilan" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{465A446E-7698-4C88-BB95-D9C31EA7A990}" name="confidentiality" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21030,7 +21012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF961E35-3C9A-4571-868D-430D15168DE6}">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -21056,12 +21038,9 @@
     <col min="21" max="21" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="28" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="80.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="66.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="56.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -21131,17 +21110,8 @@
       <c r="W1" t="s">
         <v>41</v>
       </c>
-      <c r="X1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>476480330</v>
       </c>
@@ -21170,7 +21140,7 @@
         <v>48635</v>
       </c>
       <c r="J2" s="38" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K2" s="38">
         <v>-1111</v>
@@ -21185,7 +21155,7 @@
         <v>-12127</v>
       </c>
       <c r="O2" s="38" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="P2" s="38">
         <v>-9344</v>
@@ -21209,16 +21179,7 @@
         <v>10</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -21272,16 +21233,16 @@
         <v>11</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -21293,25 +21254,25 @@
         <f t="array" ref="B11">_xlfn.UNIQUE(Performance[siren])</f>
         <v>476480330</v>
       </c>
-      <c r="C11" s="44" t="str" cm="1">
-        <f t="array" ref="C11">INDEX(Performance[Entreprises.Nom],MATCH(_xlfn.ANCHORARRAY($B$11),Performance[siren],0))</f>
-        <v>LUTTI</v>
-      </c>
-      <c r="D11" s="44" t="str" cm="1">
-        <f t="array" ref="D11">INDEX(Performance[Entreprises.Activité],MATCH(_xlfn.ANCHORARRAY($B$11),Performance[siren],0))</f>
-        <v>Fabrication d'autres produits alimentaires</v>
-      </c>
-      <c r="E11" s="44" t="str" cm="1">
-        <f t="array" ref="E11">INDEX(Performance[Entreprises.Activité détaillée],MATCH(_xlfn.ANCHORARRAY($B$11),Performance[siren],0))</f>
-        <v>Fabrication de cacao, chocolat et de produits de confiserie</v>
+      <c r="C11" s="44" t="e" cm="1">
+        <f t="array" ref="C11">INDEX(#REF!,MATCH(_xlfn.ANCHORARRAY($B$11),Performance[siren],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" s="44" t="e" cm="1">
+        <f t="array" ref="D11">INDEX(#REF!,MATCH(_xlfn.ANCHORARRAY($B$11),Performance[siren],0))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="44" t="e" cm="1">
+        <f t="array" ref="E11">INDEX(#REF!,MATCH(_xlfn.ANCHORARRAY($B$11),Performance[siren],0))</f>
+        <v>#REF!</v>
       </c>
       <c r="F11" cm="1">
         <f t="array" ref="F11:F676">SUMIFS(Performance[Chiffre_d_affaires],Performance[siren],Listes!$B$11:$B$676)</f>
         <v>64657526</v>
       </c>
-      <c r="H11" s="21" cm="1">
-        <f t="array" ref="H11">_xlfn.SORTBY(_xlfn._xlws.FILTER(Performance[date_cloture_exercice],Performance[Entreprises.Nom]=Entreprise),_xlfn._xlws.FILTER(Performance[date_cloture_exercice],Performance[Entreprises.Nom]=Entreprise),1)</f>
-        <v>44196</v>
+      <c r="H11" s="21" t="e" cm="1">
+        <f t="array" ref="H11">_xlfn.SORTBY(_xlfn._xlws.FILTER(Performance[date_cloture_exercice],#REF!=Entreprise),_xlfn._xlws.FILTER(Performance[date_cloture_exercice],#REF!=Entreprise),1)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -27370,442 +27331,442 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
         <v>79</v>
       </c>
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
         <v>83</v>
       </c>
-      <c r="B5" t="s">
-        <v>84</v>
-      </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
         <v>92</v>
       </c>
-      <c r="B13" t="s">
-        <v>94</v>
-      </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
         <v>101</v>
       </c>
-      <c r="B21" t="s">
-        <v>103</v>
-      </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
         <v>107</v>
       </c>
-      <c r="B26" t="s">
-        <v>109</v>
-      </c>
       <c r="C26" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" t="s">
         <v>113</v>
       </c>
-      <c r="B31" t="s">
-        <v>115</v>
-      </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" t="s">
         <v>118</v>
       </c>
-      <c r="B35" t="s">
-        <v>120</v>
-      </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
         <v>123</v>
       </c>
-      <c r="B39" t="s">
-        <v>125</v>
-      </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -27847,14 +27808,14 @@
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C5" s="37" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="37" t="str">
+        <v>132</v>
+      </c>
+      <c r="E5" s="37" t="e">
         <f>IF(OR(Balises!$E$8&gt;=1,Balises!$E$9&gt;=1),Balises!$E$2,"")</f>
-        <v/>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.35">
@@ -27864,77 +27825,77 @@
       <c r="D6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="11" t="str">
+      <c r="E6" s="11" t="e">
         <f>s_produit</f>
-        <v>LUTTI</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="29">
-        <f>INDEX(Performance[siren],MATCH(Entreprise,Performance[Entreprises.Nom],0))</f>
-        <v>476480330</v>
+      <c r="E7" s="29" t="e">
+        <f>INDEX(Performance[siren],MATCH(Entreprise,#REF!,0))</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C8" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="27" t="e">
         <f>Analyse!$AA$4</f>
-        <v>-9.3437831196943724E-2</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C9" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="E9" s="27">
+        <v>157</v>
+      </c>
+      <c r="E9" s="27" t="e">
         <f>Analyse!$AA$5</f>
-        <v>-4.5226629920854071E-2</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C10" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E10" s="26">
-        <f>SUMIFS(Performance[Resultat_net],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],Analyse!$E$3)</f>
-        <v>-2924242</v>
+        <v>158</v>
+      </c>
+      <c r="E10" s="26" t="e">
+        <f>SUMIFS(Performance[Resultat_net],#REF!,Entreprise,Performance[date_cloture_exercice],Analyse!$E$3)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C11" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="26">
+        <v>155</v>
+      </c>
+      <c r="E11" s="26" t="e">
         <f>INDEX(_xlfn.ANCHORARRAY(Analyse!$C$7),MATCH($E$15,_xlfn.ANCHORARRAY(Analyse!$E$7),0))</f>
-        <v>64657526</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C12" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" s="31" t="str">
         <f>Analyse!$G$4</f>
@@ -27943,10 +27904,10 @@
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C13" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="31" t="str">
         <f>Analyse!$R$4</f>
@@ -27955,56 +27916,56 @@
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C14" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="32">
+        <v>60</v>
+      </c>
+      <c r="E14" s="32" t="e">
         <f>MIN(_xlfn.ANCHORARRAY(Analyse!$E$7))</f>
-        <v>2020</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C15" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="32">
+        <v>61</v>
+      </c>
+      <c r="E15" s="32" t="e">
         <f>MAX(_xlfn.ANCHORARRAY(Analyse!$E$7))</f>
-        <v>2020</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C16" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D16" s="12"/>
-      <c r="E16" s="32" t="str">
-        <f>INDEX(Performance[Entreprises.Activité],MATCH(siren,Performance[siren],0))</f>
-        <v>Fabrication d'autres produits alimentaires</v>
+      <c r="E16" s="32" t="e">
+        <f>INDEX(#REF!,MATCH(siren,Performance[siren],0))</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C17" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D17" s="12"/>
-      <c r="E17" s="32" t="str">
-        <f>INDEX(Performance[Entreprises.Activité détaillée],MATCH(siren,Performance[siren],0))</f>
-        <v>Fabrication de cacao, chocolat et de produits de confiserie</v>
+      <c r="E17" s="32" t="e">
+        <f>INDEX(#REF!,MATCH(siren,Performance[siren],0))</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C18" s="12" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D18" s="12"/>
-      <c r="E18" s="32" t="str">
+      <c r="E18" s="32" t="e">
         <f>INDEX(Image!$C:$C,MATCH($E$17,Image!B:B,0))</f>
-        <v>Cacao</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.35">
@@ -28012,11 +27973,11 @@
         <v>5</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="20">
         <f ca="1">TODAY()</f>
-        <v>45934</v>
+        <v>45935</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.35">
@@ -28064,7 +28025,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.35">
@@ -28072,7 +28033,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
@@ -28099,9 +28060,9 @@
       <c r="D6" s="17">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="str" cm="1">
+      <c r="E6" s="15" t="e" cm="1">
         <f t="array" ref="E6">INDEX(Listes!$C$11:$C$676,Loop[[#This Row],[Itération]])</f>
-        <v>LUTTI</v>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -28133,250 +28094,250 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:37" x14ac:dyDescent="0.4">
-      <c r="E2" s="34">
+      <c r="E2" s="34" t="e">
         <f>MIN(_xlfn.ANCHORARRAY(B7))</f>
-        <v>44196</v>
-      </c>
-      <c r="F2" s="24">
+        <v>#REF!</v>
+      </c>
+      <c r="F2" s="24" t="e">
         <f>MIN(_xlfn.ANCHORARRAY($E$7))</f>
-        <v>2020</v>
-      </c>
-      <c r="G2" s="28">
+        <v>#REF!</v>
+      </c>
+      <c r="G2" s="28" t="e">
         <f>INDEX(_xlfn.ANCHORARRAY(C$7),MATCH(F2,_xlfn.ANCHORARRAY(E$7),0))</f>
-        <v>64657526</v>
-      </c>
-      <c r="Q2" s="24">
+        <v>#REF!</v>
+      </c>
+      <c r="Q2" s="24" t="e">
         <f>MIN(_xlfn.ANCHORARRAY($E$7))</f>
-        <v>2020</v>
-      </c>
-      <c r="R2" s="28">
+        <v>#REF!</v>
+      </c>
+      <c r="R2" s="28" t="e">
         <f>INDEX(_xlfn.ANCHORARRAY(N$7),MATCH(Q2,_xlfn.ANCHORARRAY(P$7),0))</f>
-        <v>-6041459</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="3" spans="2:37" x14ac:dyDescent="0.4">
-      <c r="E3" s="34">
+      <c r="E3" s="34" t="e">
         <f>MAX(_xlfn.ANCHORARRAY(B7))</f>
-        <v>44196</v>
-      </c>
-      <c r="F3" s="24">
+        <v>#REF!</v>
+      </c>
+      <c r="F3" s="24" t="e">
         <f>MAX(_xlfn.ANCHORARRAY($E$7))</f>
-        <v>2020</v>
-      </c>
-      <c r="G3" s="28">
+        <v>#REF!</v>
+      </c>
+      <c r="G3" s="28" t="e">
         <f>INDEX(_xlfn.ANCHORARRAY(C$7),MATCH(F3,_xlfn.ANCHORARRAY(E$7),0))</f>
-        <v>64657526</v>
-      </c>
-      <c r="Q3" s="24">
+        <v>#REF!</v>
+      </c>
+      <c r="Q3" s="24" t="e">
         <f>MAX(_xlfn.ANCHORARRAY($E$7))</f>
-        <v>2020</v>
-      </c>
-      <c r="R3" s="28">
+        <v>#REF!</v>
+      </c>
+      <c r="R3" s="28" t="e">
         <f>INDEX(_xlfn.ANCHORARRAY(N$7),MATCH(Q3,_xlfn.ANCHORARRAY(P$7),0))</f>
-        <v>-6041459</v>
+        <v>#REF!</v>
       </c>
       <c r="AH3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>73</v>
       </c>
-      <c r="AI3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>74</v>
       </c>
-      <c r="AK3" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="4" spans="2:37" x14ac:dyDescent="0.4">
-      <c r="B4" s="22" t="str">
+      <c r="B4" s="22" t="e">
         <f>Entreprise</f>
-        <v>LUTTI</v>
-      </c>
-      <c r="F4" s="24" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="F4" s="24" t="e">
         <f>"CAGR entre "&amp;$F$2&amp;" et "&amp;$F$3</f>
-        <v>CAGR entre 2020 et 2020</v>
+        <v>#REF!</v>
       </c>
       <c r="G4" s="31" t="str">
         <f>IFERROR((G3/G2)^(1/(F3-F2))-1,"NA")</f>
         <v>NA</v>
       </c>
-      <c r="M4" s="22" t="str">
+      <c r="M4" s="22" t="e">
         <f>Entreprise</f>
-        <v>LUTTI</v>
-      </c>
-      <c r="Q4" s="24" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="Q4" s="24" t="e">
         <f>"CAGR entre "&amp;$F$2&amp;" et "&amp;$F$3</f>
-        <v>CAGR entre 2020 et 2020</v>
+        <v>#REF!</v>
       </c>
       <c r="R4" s="31" t="str">
         <f>IFERROR((R3/R2)^(1/(Q3-Q2))-1,"NA")</f>
         <v>NA</v>
       </c>
       <c r="Z4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA4" s="33">
-        <f>SUMIFS(Performance[EBE],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)/
-SUMIFS(Performance[Chiffre_d_affaires],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)</f>
-        <v>-9.3437831196943724E-2</v>
-      </c>
-      <c r="AB4" s="30">
+        <v>69</v>
+      </c>
+      <c r="AA4" s="33" t="e">
+        <f>SUMIFS(Performance[EBE],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)/
+SUMIFS(Performance[Chiffre_d_affaires],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB4" s="30" t="e">
         <f>1-AA4</f>
-        <v>1.0934378311969437</v>
+        <v>#REF!</v>
       </c>
       <c r="AE4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF4" s="28">
-        <f>SUMIFS(Performance[Chiffre_d_affaires],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)</f>
-        <v>64657526</v>
-      </c>
-      <c r="AG4" s="35">
+        <v>46</v>
+      </c>
+      <c r="AF4" s="28" t="e">
+        <f>SUMIFS(Performance[Chiffre_d_affaires],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AG4" s="35" t="e">
         <f t="shared" ref="AG4:AG10" si="0">AF4/$AF$4</f>
-        <v>1</v>
-      </c>
-      <c r="AH4" s="3">
+        <v>#REF!</v>
+      </c>
+      <c r="AH4" s="3" t="e">
         <f>AG4</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="2:37" x14ac:dyDescent="0.4">
       <c r="Z5" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA5" s="33">
-        <f>SUMIFS(Performance[Resultat_net],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)/
-SUMIFS(Performance[Chiffre_d_affaires],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)</f>
-        <v>-4.5226629920854071E-2</v>
-      </c>
-      <c r="AB5" s="30">
+        <v>68</v>
+      </c>
+      <c r="AA5" s="33" t="e">
+        <f>SUMIFS(Performance[Resultat_net],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)/
+SUMIFS(Performance[Chiffre_d_affaires],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB5" s="30" t="e">
         <f>1-AA5</f>
-        <v>1.0452266299208541</v>
+        <v>#REF!</v>
       </c>
       <c r="AE5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF5" s="28">
+        <v>75</v>
+      </c>
+      <c r="AF5" s="28" t="e">
         <f>AF6-AF4</f>
-        <v>-29769435</v>
-      </c>
-      <c r="AG5" s="35">
+        <v>#REF!</v>
+      </c>
+      <c r="AG5" s="35" t="e">
         <f t="shared" si="0"/>
-        <v>-0.46041716783286757</v>
-      </c>
-      <c r="AI5" s="3">
+        <v>#REF!</v>
+      </c>
+      <c r="AI5" s="3" t="e">
         <f>AH6</f>
-        <v>0.53958283216713243</v>
-      </c>
-      <c r="AJ5">
+        <v>#REF!</v>
+      </c>
+      <c r="AJ5" t="e">
         <f>IF($AG5&gt;0,$AG5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AK5" s="36">
+        <v>#REF!</v>
+      </c>
+      <c r="AK5" s="36" t="e">
         <f>ABS(IF($AG5&lt;0,$AG5,0))</f>
-        <v>0.46041716783286757</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="2:37" x14ac:dyDescent="0.4">
       <c r="B6" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="E6" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="F6" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="H6" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>51</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>52</v>
       </c>
       <c r="K6" s="24"/>
       <c r="M6" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="26" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="24" t="s">
+      <c r="Q6" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Q6" s="26" t="s">
+      <c r="R6" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="R6" s="24" t="s">
+      <c r="S6" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" s="24" t="s">
         <v>51</v>
-      </c>
-      <c r="S6" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="T6" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="U6" s="24" t="s">
-        <v>52</v>
       </c>
       <c r="V6" s="24" t="s">
         <v>23</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AE6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF6" s="28">
-        <f>SUMIFS(Performance[Marge_brute],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)</f>
-        <v>34888091</v>
-      </c>
-      <c r="AG6" s="35">
+        <v>70</v>
+      </c>
+      <c r="AF6" s="28" t="e">
+        <f>SUMIFS(Performance[Marge_brute],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AG6" s="35" t="e">
         <f t="shared" si="0"/>
-        <v>0.53958283216713243</v>
-      </c>
-      <c r="AH6" s="3">
+        <v>#REF!</v>
+      </c>
+      <c r="AH6" s="3" t="e">
         <f>AG6</f>
-        <v>0.53958283216713243</v>
+        <v>#REF!</v>
       </c>
       <c r="AK6" s="36"/>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.4">
-      <c r="B7" s="25" cm="1">
+      <c r="B7" s="25" t="e" cm="1">
         <f t="array" ref="B7">Années</f>
-        <v>44196</v>
-      </c>
-      <c r="C7" s="26" cm="1">
-        <f t="array" ref="C7">SUMIFS(Performance[Chiffre_d_affaires],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],_xlfn.ANCHORARRAY($B7))</f>
-        <v>64657526</v>
-      </c>
-      <c r="D7" s="24" cm="1">
+        <v>#REF!</v>
+      </c>
+      <c r="C7" s="26" t="e" cm="1">
+        <f t="array" ref="C7">SUMIFS(Performance[Chiffre_d_affaires],#REF!,Entreprise,Performance[date_cloture_exercice],_xlfn.ANCHORARRAY($B7))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D7" s="24" t="e" cm="1">
         <f t="array" ref="D7">IF(_xlfn.ANCHORARRAY($E$7)=$F$2,0,IFERROR(YEAR(INDEX(_xlfn.ANCHORARRAY(B7),_xlfn.SEQUENCE(COUNTA(_xlfn.ANCHORARRAY($B$7)))-1)),0))</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="24" cm="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="24" t="e" cm="1">
         <f t="array" ref="E7">YEAR(_xlfn.ANCHORARRAY(B7))</f>
-        <v>2020</v>
-      </c>
-      <c r="F7" s="28" cm="1">
+        <v>#REF!</v>
+      </c>
+      <c r="F7" s="28" t="e" cm="1">
         <f t="array" ref="F7">IF(_xlfn.ANCHORARRAY($E$7)=$F$2,0,IFERROR(INDEX(_xlfn.ANCHORARRAY($C$7),_xlfn.SEQUENCE(COUNTA(_xlfn.ANCHORARRAY($B$7)))-1),0))</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="G7" s="27" cm="1">
         <f t="array" ref="G7">IFERROR((_xlfn.ANCHORARRAY(C7)/_xlfn.ANCHORARRAY(F7))^(1/(_xlfn.ANCHORARRAY(E7)-_xlfn.ANCHORARRAY(D7)))-1,0)</f>
@@ -28390,31 +28351,31 @@
         <f t="array" ref="I7">IF(_xlfn.ANCHORARRAY(G7)&lt;0,1,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="J7" t="str" cm="1">
+      <c r="J7" t="e" cm="1">
         <f t="array" ref="J7">IF(((_xlfn.ANCHORARRAY(E7)=_xlfn.ANCHORARRAY(D7)+1)+(_xlfn.ANCHORARRAY(D7)=0)&gt;0),"","CAGR "&amp;_xlfn.ANCHORARRAY(D7)&amp;"
 ")&amp;TEXT(_xlfn.ANCHORARRAY(G7),"+0%;-0%;-")</f>
-        <v>-</v>
+        <v>#REF!</v>
       </c>
       <c r="K7" s="28"/>
-      <c r="M7" s="25" cm="1">
+      <c r="M7" s="25" t="e" cm="1">
         <f t="array" ref="M7">Années</f>
-        <v>44196</v>
-      </c>
-      <c r="N7" s="26" cm="1">
-        <f t="array" ref="N7">SUMIFS(Performance[EBE],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],_xlfn.ANCHORARRAY($B7))</f>
-        <v>-6041459</v>
-      </c>
-      <c r="O7" s="24" cm="1">
+        <v>#REF!</v>
+      </c>
+      <c r="N7" s="26" t="e" cm="1">
+        <f t="array" ref="N7">SUMIFS(Performance[EBE],#REF!,Entreprise,Performance[date_cloture_exercice],_xlfn.ANCHORARRAY($B7))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O7" s="24" t="e" cm="1">
         <f t="array" ref="O7">IF(_xlfn.ANCHORARRAY($E$7)=$F$2,0,IFERROR(YEAR(INDEX(_xlfn.ANCHORARRAY(M7),_xlfn.SEQUENCE(COUNTA(_xlfn.ANCHORARRAY($B$7)))-1)),0))</f>
-        <v>0</v>
-      </c>
-      <c r="P7" s="24" cm="1">
+        <v>#REF!</v>
+      </c>
+      <c r="P7" s="24" t="e" cm="1">
         <f t="array" ref="P7">YEAR(_xlfn.ANCHORARRAY(M7))</f>
-        <v>2020</v>
-      </c>
-      <c r="Q7" s="28" cm="1">
+        <v>#REF!</v>
+      </c>
+      <c r="Q7" s="28" t="e" cm="1">
         <f t="array" ref="Q7">IF(_xlfn.ANCHORARRAY(P7)=$F$2,0,IFERROR(INDEX(_xlfn.ANCHORARRAY(N7),_xlfn.SEQUENCE(COUNTA(_xlfn.ANCHORARRAY(M7)))-1),0))</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="R7" s="27" cm="1">
         <f t="array" ref="R7">IFERROR((_xlfn.ANCHORARRAY(N7)/_xlfn.ANCHORARRAY(Q7))^(1/(_xlfn.ANCHORARRAY(P7)-_xlfn.ANCHORARRAY(O7)))-1,0)</f>
@@ -28428,41 +28389,41 @@
         <f t="array" ref="T7">IF(_xlfn.ANCHORARRAY(R7)&lt;0,1,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="U7" t="str" cm="1">
+      <c r="U7" t="e" cm="1">
         <f t="array" ref="U7">IF(((_xlfn.ANCHORARRAY(P7)=_xlfn.ANCHORARRAY(O7)+1)+(_xlfn.ANCHORARRAY(O7)=0)&gt;0),"","CAGR "&amp;_xlfn.ANCHORARRAY(O7)&amp;"
 ")&amp;TEXT(_xlfn.ANCHORARRAY(R7),"+0%;-0%;-")</f>
-        <v>-</v>
-      </c>
-      <c r="V7" s="28" cm="1">
-        <f t="array" ref="V7">SUMIFS(Performance[EBE],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],_xlfn.ANCHORARRAY($B7))</f>
-        <v>-6041459</v>
-      </c>
-      <c r="W7" s="3" cm="1">
+        <v>#REF!</v>
+      </c>
+      <c r="V7" s="28" t="e" cm="1">
+        <f t="array" ref="V7">SUMIFS(Performance[EBE],#REF!,Entreprise,Performance[date_cloture_exercice],_xlfn.ANCHORARRAY($B7))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W7" s="3" t="e" cm="1">
         <f t="array" ref="W7">_xlfn.ANCHORARRAY(V7)/_xlfn.ANCHORARRAY(C7)</f>
-        <v>-9.3437831196943724E-2</v>
+        <v>#REF!</v>
       </c>
       <c r="AE7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF7" s="28">
+        <v>76</v>
+      </c>
+      <c r="AF7" s="28" t="e">
         <f>AF8-AF6</f>
-        <v>-40929550</v>
-      </c>
-      <c r="AG7" s="35">
+        <v>#REF!</v>
+      </c>
+      <c r="AG7" s="35" t="e">
         <f t="shared" si="0"/>
-        <v>-0.63302066336407614</v>
-      </c>
-      <c r="AI7" s="3">
+        <v>#REF!</v>
+      </c>
+      <c r="AI7" s="3" t="e">
         <f>AH8</f>
-        <v>-9.3437831196943724E-2</v>
-      </c>
-      <c r="AJ7">
+        <v>#REF!</v>
+      </c>
+      <c r="AJ7" t="e">
         <f>IF($AG7&gt;0,$AG7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AK7" s="36">
+        <v>#REF!</v>
+      </c>
+      <c r="AK7" s="36" t="e">
         <f>ABS(IF($AG7&lt;0,$AG7,0))</f>
-        <v>0.63302066336407614</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="8" spans="2:37" x14ac:dyDescent="0.4">
@@ -28485,17 +28446,17 @@
       <c r="AE8" t="s">
         <v>23</v>
       </c>
-      <c r="AF8" s="28">
-        <f>SUMIFS(Performance[EBE],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)</f>
-        <v>-6041459</v>
-      </c>
-      <c r="AG8" s="35">
+      <c r="AF8" s="28" t="e">
+        <f>SUMIFS(Performance[EBE],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AG8" s="35" t="e">
         <f t="shared" si="0"/>
-        <v>-9.3437831196943724E-2</v>
-      </c>
-      <c r="AH8" s="3">
+        <v>#REF!</v>
+      </c>
+      <c r="AH8" s="3" t="e">
         <f>AG8</f>
-        <v>-9.3437831196943724E-2</v>
+        <v>#REF!</v>
       </c>
       <c r="AK8" s="36"/>
     </row>
@@ -28517,27 +28478,27 @@
       <c r="T9" s="24"/>
       <c r="V9" s="28"/>
       <c r="AE9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF9" s="28">
+        <v>77</v>
+      </c>
+      <c r="AF9" s="28" t="e">
         <f>AF10-AF8</f>
-        <v>3117217</v>
-      </c>
-      <c r="AG9" s="35">
+        <v>#REF!</v>
+      </c>
+      <c r="AG9" s="35" t="e">
         <f t="shared" si="0"/>
-        <v>4.8211201276089653E-2</v>
-      </c>
-      <c r="AI9" s="3">
+        <v>#REF!</v>
+      </c>
+      <c r="AI9" s="3" t="e">
         <f>AH10</f>
-        <v>-4.5226629920854071E-2</v>
-      </c>
-      <c r="AJ9">
+        <v>#REF!</v>
+      </c>
+      <c r="AJ9" t="e">
         <f>IF($AG9&gt;0,$AG9,0)</f>
-        <v>4.8211201276089653E-2</v>
-      </c>
-      <c r="AK9" s="36">
+        <v>#REF!</v>
+      </c>
+      <c r="AK9" s="36" t="e">
         <f>ABS(IF($AG9&lt;0,$AG9,0))</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="10" spans="2:37" x14ac:dyDescent="0.4">
@@ -28558,19 +28519,19 @@
       <c r="T10" s="24"/>
       <c r="V10" s="28"/>
       <c r="AE10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF10" s="28">
-        <f>SUMIFS(Performance[Resultat_net],Performance[Entreprises.Nom],Entreprise,Performance[date_cloture_exercice],$E$3)</f>
-        <v>-2924242</v>
-      </c>
-      <c r="AG10" s="35">
+        <v>68</v>
+      </c>
+      <c r="AF10" s="28" t="e">
+        <f>SUMIFS(Performance[Resultat_net],#REF!,Entreprise,Performance[date_cloture_exercice],$E$3)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AG10" s="35" t="e">
         <f t="shared" si="0"/>
-        <v>-4.5226629920854071E-2</v>
-      </c>
-      <c r="AH10" s="3">
+        <v>#REF!</v>
+      </c>
+      <c r="AH10" s="3" t="e">
         <f>AG10</f>
-        <v>-4.5226629920854071E-2</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.4">
